--- a/wedding_forms/019_wedding_show_giveaway_entry--wedding_forms.xlsx
+++ b/wedding_forms/019_wedding_show_giveaway_entry--wedding_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>event_coordinator</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Event Coordinator</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>president</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>president</t>
+          <t>representative</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Representative</t>
         </is>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>representative</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_title_choices</t>
+          <t>attendees_interests_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>catering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Catering</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>catering</t>
+          <t>event_services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Catering</t>
+          <t>Event Services</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_services</t>
+          <t>music_and_entertainment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event Services</t>
+          <t>Music and Entertainment</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>music_and_entertainment</t>
+          <t>photography_and_videography</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Music and Entertainment</t>
+          <t>Photography and Videography</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>photography_and_videography</t>
+          <t>printing_and_stationery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Photography and Videography</t>
+          <t>Printing and Stationery</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>printing_and_stationery</t>
+          <t>wedding_dresses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Printing and Stationery</t>
+          <t>Wedding Dresses</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wedding_dresses</t>
+          <t>wedding_invitations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wedding Dresses</t>
+          <t>Wedding Invitations</t>
         </is>
       </c>
     </row>
@@ -1373,27 +1373,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wedding_invitations</t>
+          <t>wedding_favors</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>Wedding Invitations</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>attendees_interests_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>wedding_favors</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Wedding Favors</t>
         </is>
